--- a/df.xlsx
+++ b/df.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stoces\Documents\Cesky_Hradek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B54E32-C8E0-4D9D-AEB6-F1E08F34BF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4D1C64D-54F0-43C2-8207-049339E6D1E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="41">
   <si>
     <t>Year</t>
   </si>
@@ -142,6 +142,12 @@
   </si>
   <si>
     <t>Q</t>
+  </si>
+  <si>
+    <t>FaithsPD</t>
+  </si>
+  <si>
+    <t>SESpd</t>
   </si>
 </sst>
 </file>
@@ -494,10 +500,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O306"/>
+  <dimension ref="A1:Q306"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -543,8 +549,14 @@
       <c r="O1" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -590,8 +602,14 @@
       <c r="O2">
         <v>1.1395160900000001</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P2">
+        <v>3.3372090000000001</v>
+      </c>
+      <c r="Q2">
+        <v>-0.37532105961282902</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -637,8 +655,14 @@
       <c r="O3">
         <v>1.78508245</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P3">
+        <v>4.1976740000000001</v>
+      </c>
+      <c r="Q3">
+        <v>0.90172804762985004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -684,8 +708,14 @@
       <c r="O4">
         <v>1.31915684</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P4">
+        <v>4.488372</v>
+      </c>
+      <c r="Q4">
+        <v>1.67374204207076</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -731,8 +761,14 @@
       <c r="O5">
         <v>1.7060643900000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P5">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q5">
+        <v>-0.86372764681821701</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -778,8 +814,14 @@
       <c r="O6">
         <v>1.49138226</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P6">
+        <v>3.6627909999999999</v>
+      </c>
+      <c r="Q6">
+        <v>-0.30073409788419803</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -825,8 +867,14 @@
       <c r="O7">
         <v>2.0287110300000002</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P7">
+        <v>3.5348839999999999</v>
+      </c>
+      <c r="Q7">
+        <v>0.164107780060648</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -872,8 +920,14 @@
       <c r="O8">
         <v>1.8473864499999999</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P8">
+        <v>2.6627909999999999</v>
+      </c>
+      <c r="Q8">
+        <v>0.69326902608079499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -919,8 +973,14 @@
       <c r="O9">
         <v>1.38146722</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P9">
+        <v>2.8255810000000001</v>
+      </c>
+      <c r="Q9">
+        <v>-0.53630770932778404</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -966,8 +1026,14 @@
       <c r="O10">
         <v>1.6786603</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P10">
+        <v>3.7906979999999999</v>
+      </c>
+      <c r="Q10">
+        <v>-3.7322343684120199E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -1013,8 +1079,14 @@
       <c r="O11">
         <v>1.4748592899999999</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P11">
+        <v>3.0930230000000001</v>
+      </c>
+      <c r="Q11">
+        <v>-0.431182443891512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -1060,8 +1132,14 @@
       <c r="O12">
         <v>1.1642721</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P12">
+        <v>3.0465119999999999</v>
+      </c>
+      <c r="Q12">
+        <v>-0.92099491636486897</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -1107,8 +1185,14 @@
       <c r="O13">
         <v>1.95890816</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P13">
+        <v>3.5697670000000001</v>
+      </c>
+      <c r="Q13">
+        <v>-0.18011772956508901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -1154,8 +1238,14 @@
       <c r="O14">
         <v>1.70334388</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P14">
+        <v>2.9767440000000001</v>
+      </c>
+      <c r="Q14">
+        <v>-0.86471996763700798</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1201,8 +1291,14 @@
       <c r="O15">
         <v>0.34774368</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P15">
+        <v>2.9302329999999999</v>
+      </c>
+      <c r="Q15">
+        <v>-0.82469798996085897</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1248,8 +1344,14 @@
       <c r="O16">
         <v>0.64717170000000002</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P16">
+        <v>3.3488370000000001</v>
+      </c>
+      <c r="Q16">
+        <v>-0.62367771389163795</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -1295,8 +1397,14 @@
       <c r="O17">
         <v>1.2673044499999999</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P17">
+        <v>4.8023259999999999</v>
+      </c>
+      <c r="Q17">
+        <v>1.5628096436724399</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1342,8 +1450,14 @@
       <c r="O18">
         <v>0.50056573999999998</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P18">
+        <v>3.8255810000000001</v>
+      </c>
+      <c r="Q18">
+        <v>-0.31718931645908099</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -1389,8 +1503,14 @@
       <c r="O19">
         <v>2.4426494600000002</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P19">
+        <v>3.4069769999999999</v>
+      </c>
+      <c r="Q19">
+        <v>0.61998942035989402</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -1436,8 +1556,14 @@
       <c r="O20">
         <v>0.65806977</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P20">
+        <v>3.0348839999999999</v>
+      </c>
+      <c r="Q20">
+        <v>4.9081664053283298E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>13</v>
       </c>
@@ -1483,8 +1609,14 @@
       <c r="O21">
         <v>1.1127329399999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P21">
+        <v>3.627907</v>
+      </c>
+      <c r="Q21">
+        <v>-3.1299141081046297E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>13</v>
       </c>
@@ -1530,8 +1662,14 @@
       <c r="O22">
         <v>0.99133914999999995</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P22">
+        <v>3.755814</v>
+      </c>
+      <c r="Q22">
+        <v>0.136752673203349</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1577,8 +1715,14 @@
       <c r="O23">
         <v>1.4564457200000001</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P23">
+        <v>4.7790699999999999</v>
+      </c>
+      <c r="Q23">
+        <v>1.2642634226520599</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>13</v>
       </c>
@@ -1624,8 +1768,14 @@
       <c r="O24">
         <v>1.76506045</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P24">
+        <v>2.744186</v>
+      </c>
+      <c r="Q24">
+        <v>-1.0037759467690199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>13</v>
       </c>
@@ -1671,8 +1821,14 @@
       <c r="O25">
         <v>1.7888278099999999</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P25">
+        <v>4.5</v>
+      </c>
+      <c r="Q25">
+        <v>1.65546168127308</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -1718,8 +1874,14 @@
       <c r="O26">
         <v>1.6064684899999999</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P26">
+        <v>2.0465119999999999</v>
+      </c>
+      <c r="Q26">
+        <v>-0.68035379663651996</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -1765,8 +1927,14 @@
       <c r="O27">
         <v>1.7491939599999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P27">
+        <v>3.0697670000000001</v>
+      </c>
+      <c r="Q27">
+        <v>-0.19112501767461601</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>13</v>
       </c>
@@ -1812,8 +1980,14 @@
       <c r="O28">
         <v>2.07428379</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P28">
+        <v>4.4069770000000004</v>
+      </c>
+      <c r="Q28">
+        <v>-3.8743571868159098E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>13</v>
       </c>
@@ -1859,8 +2033,14 @@
       <c r="O29">
         <v>1.7923128800000001</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P29">
+        <v>2.988372</v>
+      </c>
+      <c r="Q29">
+        <v>-0.93304428584935195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>13</v>
       </c>
@@ -1906,8 +2086,14 @@
       <c r="O30">
         <v>2.0313234200000001</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P30">
+        <v>3.767442</v>
+      </c>
+      <c r="Q30">
+        <v>-0.18744661059446699</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>13</v>
       </c>
@@ -1953,8 +2139,14 @@
       <c r="O31">
         <v>1.8838909500000001</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P31">
+        <v>3.5697670000000001</v>
+      </c>
+      <c r="Q31">
+        <v>0.69660619007726399</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>13</v>
       </c>
@@ -2000,8 +2192,14 @@
       <c r="O32">
         <v>2.0031347300000002</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P32">
+        <v>4.1046509999999996</v>
+      </c>
+      <c r="Q32">
+        <v>-6.3888114997846301E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>13</v>
       </c>
@@ -2047,8 +2245,14 @@
       <c r="O33">
         <v>0.44662675000000002</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P33">
+        <v>2.872093</v>
+      </c>
+      <c r="Q33">
+        <v>-0.53857935215389097</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>13</v>
       </c>
@@ -2094,8 +2298,14 @@
       <c r="O34">
         <v>0.98088702999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P34">
+        <v>2.9651160000000001</v>
+      </c>
+      <c r="Q34">
+        <v>-0.60298173135149202</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -2141,8 +2351,14 @@
       <c r="O35">
         <v>1.6428620700000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P35">
+        <v>3.360465</v>
+      </c>
+      <c r="Q35">
+        <v>0.55539938042130299</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -2188,8 +2404,14 @@
       <c r="O36">
         <v>0.33480617000000001</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P36">
+        <v>2.9767440000000001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.66302976386002699</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -2235,8 +2457,14 @@
       <c r="O37">
         <v>2.3931156200000001</v>
       </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P37">
+        <v>5.1627910000000004</v>
+      </c>
+      <c r="Q37">
+        <v>1.40480670306531</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -2282,8 +2510,14 @@
       <c r="O38">
         <v>1.6241146099999999</v>
       </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P38">
+        <v>3.116279</v>
+      </c>
+      <c r="Q38">
+        <v>0.227042470262864</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -2329,8 +2563,14 @@
       <c r="O39">
         <v>1.56227385</v>
       </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P39">
+        <v>5.5</v>
+      </c>
+      <c r="Q39">
+        <v>1.9547496970151299</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -2376,8 +2616,14 @@
       <c r="O40">
         <v>1.35289364</v>
       </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P40">
+        <v>4.0813949999999997</v>
+      </c>
+      <c r="Q40">
+        <v>0.16828143423175901</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -2423,8 +2669,14 @@
       <c r="O41">
         <v>1.69986712</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P41">
+        <v>3.732558</v>
+      </c>
+      <c r="Q41">
+        <v>0.75385633739808899</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -2470,8 +2722,14 @@
       <c r="O42">
         <v>1.3766968900000001</v>
       </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P42">
+        <v>3.0465119999999999</v>
+      </c>
+      <c r="Q42">
+        <v>-0.91825130745793404</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -2517,8 +2775,14 @@
       <c r="O43">
         <v>1.7119840900000001</v>
       </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P43">
+        <v>2.0697670000000001</v>
+      </c>
+      <c r="Q43">
+        <v>-0.59128029592012399</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -2564,8 +2828,14 @@
       <c r="O44">
         <v>1.7671074899999999</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P44">
+        <v>3.732558</v>
+      </c>
+      <c r="Q44">
+        <v>1.3764561122786501</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -2611,8 +2881,14 @@
       <c r="O45">
         <v>1.8075473799999999</v>
       </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P45">
+        <v>4.1511630000000004</v>
+      </c>
+      <c r="Q45">
+        <v>1.4842638795590499</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -2658,8 +2934,14 @@
       <c r="O46">
         <v>1.70686125</v>
       </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P46">
+        <v>2.883721</v>
+      </c>
+      <c r="Q46">
+        <v>-0.48703074251815598</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -2705,8 +2987,14 @@
       <c r="O47">
         <v>1.6815542999999999</v>
       </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P47">
+        <v>3.0465119999999999</v>
+      </c>
+      <c r="Q47">
+        <v>-0.72342303328701196</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -2752,8 +3040,14 @@
       <c r="O48">
         <v>1.79500587</v>
       </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P48">
+        <v>3.4651160000000001</v>
+      </c>
+      <c r="Q48">
+        <v>0.88753340871311004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -2799,8 +3093,14 @@
       <c r="O49">
         <v>1.6460838900000001</v>
       </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P49">
+        <v>3.3372090000000001</v>
+      </c>
+      <c r="Q49">
+        <v>-0.481891057032512</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -2846,8 +3146,14 @@
       <c r="O50">
         <v>1.08663669</v>
       </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P50">
+        <v>3.744186</v>
+      </c>
+      <c r="Q50">
+        <v>7.0811279118005901E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -2893,8 +3199,14 @@
       <c r="O51">
         <v>1.1809080999999999</v>
       </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P51">
+        <v>2.3023259999999999</v>
+      </c>
+      <c r="Q51">
+        <v>-0.948087425783678</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -2940,8 +3252,14 @@
       <c r="O52">
         <v>1.26952935</v>
       </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P52">
+        <v>2.1744189999999999</v>
+      </c>
+      <c r="Q52">
+        <v>-0.38501168018388698</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -2987,8 +3305,14 @@
       <c r="O53">
         <v>1.48684262</v>
       </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P53">
+        <v>3.116279</v>
+      </c>
+      <c r="Q53">
+        <v>-0.78972351394047402</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -3034,8 +3358,14 @@
       <c r="O54">
         <v>0.57772210999999996</v>
       </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P54">
+        <v>3.0930230000000001</v>
+      </c>
+      <c r="Q54">
+        <v>-0.68989581247529597</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -3081,8 +3411,14 @@
       <c r="O55">
         <v>1.70243473</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P55">
+        <v>3.5348839999999999</v>
+      </c>
+      <c r="Q55">
+        <v>3.7547646704342498E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -3128,8 +3464,14 @@
       <c r="O56">
         <v>0.52209905000000001</v>
       </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P56">
+        <v>2.511628</v>
+      </c>
+      <c r="Q56">
+        <v>-0.94058434637668797</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -3175,8 +3517,14 @@
       <c r="O57">
         <v>0.23872209999999999</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P57">
+        <v>2.895349</v>
+      </c>
+      <c r="Q57">
+        <v>0.24291032214682001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -3222,8 +3570,14 @@
       <c r="O58">
         <v>0.27179881</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P58">
+        <v>2.232558</v>
+      </c>
+      <c r="Q58">
+        <v>-1.1871127791851399</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -3269,8 +3623,14 @@
       <c r="O59">
         <v>1.7831913399999999</v>
       </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P59">
+        <v>3.372093</v>
+      </c>
+      <c r="Q59">
+        <v>1.2184049432194799</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -3316,8 +3676,14 @@
       <c r="O60">
         <v>0.97065245</v>
       </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P60">
+        <v>2.372093</v>
+      </c>
+      <c r="Q60">
+        <v>-1.1473009648556101</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -3363,8 +3729,14 @@
       <c r="O61">
         <v>1.4316262500000001</v>
       </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P61">
+        <v>1.6744190000000001</v>
+      </c>
+      <c r="Q61">
+        <v>0.115154694924459</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -3410,8 +3782,14 @@
       <c r="O62">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -3457,8 +3835,14 @@
       <c r="O63">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -3504,8 +3888,14 @@
       <c r="O64">
         <v>1.1835397700000001</v>
       </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P64">
+        <v>2.0581399999999999</v>
+      </c>
+      <c r="Q64">
+        <v>0.155961115442147</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -3551,8 +3941,14 @@
       <c r="O65">
         <v>1.0748435199999999</v>
       </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P65">
+        <v>2.5465119999999999</v>
+      </c>
+      <c r="Q65">
+        <v>4.7281108671081498E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -3598,8 +3994,14 @@
       <c r="O66">
         <v>1.6499258000000001</v>
       </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P66">
+        <v>2.7906979999999999</v>
+      </c>
+      <c r="Q66">
+        <v>3.7216521912139498E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -3645,8 +4047,14 @@
       <c r="O67">
         <v>0.53718116999999999</v>
       </c>
-    </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P67">
+        <v>2.7790699999999999</v>
+      </c>
+      <c r="Q67">
+        <v>0.47778830703794301</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -3692,8 +4100,14 @@
       <c r="O68">
         <v>0.75368541</v>
       </c>
-    </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P68">
+        <v>2.988372</v>
+      </c>
+      <c r="Q68">
+        <v>5.2341041639487502E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -3739,8 +4153,14 @@
       <c r="O69">
         <v>7.0696609999999993E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P69">
+        <v>1.0465120000000001</v>
+      </c>
+      <c r="Q69">
+        <v>-1.21458119794873</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>13</v>
       </c>
@@ -3786,8 +4206,14 @@
       <c r="O70">
         <v>1.01793888</v>
       </c>
-    </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P70">
+        <v>1.9069769999999999</v>
+      </c>
+      <c r="Q70">
+        <v>0.61844506649698205</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -3833,8 +4259,14 @@
       <c r="O71">
         <v>1.46030942</v>
       </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P71">
+        <v>2.6744189999999999</v>
+      </c>
+      <c r="Q71">
+        <v>0.82948028546172003</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -3880,8 +4312,14 @@
       <c r="O72">
         <v>0.41635782999999998</v>
       </c>
-    </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P72">
+        <v>2.2790699999999999</v>
+      </c>
+      <c r="Q72">
+        <v>-0.12765896699018001</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -3927,8 +4365,14 @@
       <c r="O73">
         <v>1.67044237</v>
       </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P73">
+        <v>3.988372</v>
+      </c>
+      <c r="Q73">
+        <v>1.85477236224036</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>32</v>
       </c>
@@ -3974,8 +4418,14 @@
       <c r="O74">
         <v>2.4840522900000002</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P74">
+        <v>3.2093020000000001</v>
+      </c>
+      <c r="Q74">
+        <v>-0.36667092046637101</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>32</v>
       </c>
@@ -4021,8 +4471,14 @@
       <c r="O75">
         <v>2.3230552100000001</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P75">
+        <v>3.488372</v>
+      </c>
+      <c r="Q75">
+        <v>-1.11034904999774</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>32</v>
       </c>
@@ -4068,8 +4524,14 @@
       <c r="O76">
         <v>1.82856018</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P76">
+        <v>3.9302329999999999</v>
+      </c>
+      <c r="Q76">
+        <v>0.55515064813786197</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>32</v>
       </c>
@@ -4115,8 +4577,14 @@
       <c r="O77">
         <v>2.1331318700000002</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P77">
+        <v>2.872093</v>
+      </c>
+      <c r="Q77">
+        <v>-8.6471155521477397E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>32</v>
       </c>
@@ -4162,8 +4630,14 @@
       <c r="O78">
         <v>1.47924184</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P78">
+        <v>3.488372</v>
+      </c>
+      <c r="Q78">
+        <v>-0.77134352723724997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>32</v>
       </c>
@@ -4209,8 +4683,14 @@
       <c r="O79">
         <v>2.6027346800000002</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P79">
+        <v>3.4767440000000001</v>
+      </c>
+      <c r="Q79">
+        <v>0.274180085928385</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>32</v>
       </c>
@@ -4256,8 +4736,14 @@
       <c r="O80">
         <v>1.6896959899999999</v>
       </c>
-    </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P80">
+        <v>2.8023259999999999</v>
+      </c>
+      <c r="Q80">
+        <v>0.47108356682797697</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>32</v>
       </c>
@@ -4303,8 +4789,14 @@
       <c r="O81">
         <v>1.62418755</v>
       </c>
-    </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P81">
+        <v>3.7093020000000001</v>
+      </c>
+      <c r="Q81">
+        <v>-6.0113855347705802E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -4350,8 +4842,14 @@
       <c r="O82">
         <v>1.7830879399999999</v>
       </c>
-    </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P82">
+        <v>5.1395350000000004</v>
+      </c>
+      <c r="Q82">
+        <v>1.11233461499046</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>32</v>
       </c>
@@ -4397,8 +4895,14 @@
       <c r="O83">
         <v>1.9331900500000001</v>
       </c>
-    </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P83">
+        <v>3.9302329999999999</v>
+      </c>
+      <c r="Q83">
+        <v>0.239011445839031</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>32</v>
       </c>
@@ -4444,8 +4948,14 @@
       <c r="O84">
         <v>2.0847444300000002</v>
       </c>
-    </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P84">
+        <v>3.8139530000000001</v>
+      </c>
+      <c r="Q84">
+        <v>0.26077281546199599</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>32</v>
       </c>
@@ -4491,8 +5001,14 @@
       <c r="O85">
         <v>2.4011659600000002</v>
       </c>
-    </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P85">
+        <v>3.383721</v>
+      </c>
+      <c r="Q85">
+        <v>0.43820521183362099</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>32</v>
       </c>
@@ -4538,8 +5054,14 @@
       <c r="O86">
         <v>1.89092773</v>
       </c>
-    </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P86">
+        <v>3.6511629999999999</v>
+      </c>
+      <c r="Q86">
+        <v>-1.53366827773651E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>32</v>
       </c>
@@ -4585,8 +5107,14 @@
       <c r="O87">
         <v>0.62494400999999999</v>
       </c>
-    </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P87">
+        <v>3.6627909999999999</v>
+      </c>
+      <c r="Q87">
+        <v>0.37181223959335902</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>32</v>
       </c>
@@ -4632,8 +5160,14 @@
       <c r="O88">
         <v>1.0037607</v>
       </c>
-    </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P88">
+        <v>2.9302329999999999</v>
+      </c>
+      <c r="Q88">
+        <v>-0.65986011611130402</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>32</v>
       </c>
@@ -4679,8 +5213,14 @@
       <c r="O89">
         <v>1.45114239</v>
       </c>
-    </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P89">
+        <v>3.6976740000000001</v>
+      </c>
+      <c r="Q89">
+        <v>-0.72486293560516502</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>32</v>
       </c>
@@ -4726,8 +5266,14 @@
       <c r="O90">
         <v>0.85171158999999996</v>
       </c>
-    </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P90">
+        <v>3.9418600000000001</v>
+      </c>
+      <c r="Q90">
+        <v>-0.145897206502446</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>32</v>
       </c>
@@ -4773,8 +5319,14 @@
       <c r="O91">
         <v>2.2665056899999998</v>
       </c>
-    </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P91">
+        <v>4.1046509999999996</v>
+      </c>
+      <c r="Q91">
+        <v>0.80456398783879701</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>32</v>
       </c>
@@ -4820,8 +5372,14 @@
       <c r="O92">
         <v>1.6320117700000001</v>
       </c>
-    </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P92">
+        <v>2.5348839999999999</v>
+      </c>
+      <c r="Q92">
+        <v>-0.886550520968998</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>32</v>
       </c>
@@ -4867,8 +5425,14 @@
       <c r="O93">
         <v>1.19610729</v>
       </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P93">
+        <v>3.4186049999999999</v>
+      </c>
+      <c r="Q93">
+        <v>-0.13293652143165899</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>32</v>
       </c>
@@ -4914,8 +5478,14 @@
       <c r="O94">
         <v>1.7705809299999999</v>
       </c>
-    </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P94">
+        <v>3.395349</v>
+      </c>
+      <c r="Q94">
+        <v>0.82826262756132896</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>32</v>
       </c>
@@ -4961,8 +5531,14 @@
       <c r="O95">
         <v>1.8049939699999999</v>
       </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P95">
+        <v>3.627907</v>
+      </c>
+      <c r="Q95">
+        <v>0.101309949200809</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>32</v>
       </c>
@@ -5008,8 +5584,14 @@
       <c r="O96">
         <v>1.6177431499999999</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P96">
+        <v>2.9767440000000001</v>
+      </c>
+      <c r="Q96">
+        <v>-0.37850891316542501</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>32</v>
       </c>
@@ -5055,8 +5637,14 @@
       <c r="O97">
         <v>1.4145975399999999</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P97">
+        <v>3.5697670000000001</v>
+      </c>
+      <c r="Q97">
+        <v>0.78877074826524696</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>32</v>
       </c>
@@ -5102,8 +5690,14 @@
       <c r="O98">
         <v>1.67760216</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P98">
+        <v>2.604651</v>
+      </c>
+      <c r="Q98">
+        <v>-1.3103120187721999</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>32</v>
       </c>
@@ -5149,8 +5743,14 @@
       <c r="O99">
         <v>1.2020639</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P99">
+        <v>3.639535</v>
+      </c>
+      <c r="Q99">
+        <v>0.60144808868680999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>32</v>
       </c>
@@ -5196,8 +5796,14 @@
       <c r="O100">
         <v>1.76760235</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P100">
+        <v>2.7790699999999999</v>
+      </c>
+      <c r="Q100">
+        <v>-1.2623850192775601</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>32</v>
       </c>
@@ -5243,8 +5849,14 @@
       <c r="O101">
         <v>1.4722392099999999</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P101">
+        <v>2.4418600000000001</v>
+      </c>
+      <c r="Q101">
+        <v>-1.0432850665632301</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>32</v>
       </c>
@@ -5290,8 +5902,14 @@
       <c r="O102">
         <v>1.9521303400000001</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P102">
+        <v>3.8255810000000001</v>
+      </c>
+      <c r="Q102">
+        <v>0.73956496201524802</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>32</v>
       </c>
@@ -5337,8 +5955,14 @@
       <c r="O103">
         <v>1.7528096399999999</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P103">
+        <v>3.488372</v>
+      </c>
+      <c r="Q103">
+        <v>0.108004484796932</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>32</v>
       </c>
@@ -5384,8 +6008,14 @@
       <c r="O104">
         <v>1.36192183</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P104">
+        <v>2.3139530000000001</v>
+      </c>
+      <c r="Q104">
+        <v>-0.60727453781205298</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>32</v>
       </c>
@@ -5431,8 +6061,14 @@
       <c r="O105">
         <v>0.90085110000000002</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P105">
+        <v>2.5581399999999999</v>
+      </c>
+      <c r="Q105">
+        <v>-1.0928644665309399</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>32</v>
       </c>
@@ -5478,8 +6114,14 @@
       <c r="O106">
         <v>1.0105177299999999</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P106">
+        <v>2.627907</v>
+      </c>
+      <c r="Q106">
+        <v>-1.2399633828927701</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>32</v>
       </c>
@@ -5525,8 +6167,14 @@
       <c r="O107">
         <v>0.70986674999999999</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P107">
+        <v>2.2790699999999999</v>
+      </c>
+      <c r="Q107">
+        <v>-1.02639780534031</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>32</v>
       </c>
@@ -5572,8 +6220,14 @@
       <c r="O108">
         <v>0.99200504</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P108">
+        <v>2.5930230000000001</v>
+      </c>
+      <c r="Q108">
+        <v>-0.320906203030769</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>32</v>
       </c>
@@ -5619,8 +6273,14 @@
       <c r="O109">
         <v>1.9142851000000001</v>
       </c>
-    </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P109">
+        <v>3.744186</v>
+      </c>
+      <c r="Q109">
+        <v>0.284581802164935</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>32</v>
       </c>
@@ -5666,8 +6326,14 @@
       <c r="O110">
         <v>0.45772326000000002</v>
       </c>
-    </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P110">
+        <v>3.5465119999999999</v>
+      </c>
+      <c r="Q110">
+        <v>0.42502142042124402</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>32</v>
       </c>
@@ -5713,8 +6379,14 @@
       <c r="O111">
         <v>2.4491405400000001</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P111">
+        <v>3.8488370000000001</v>
+      </c>
+      <c r="Q111">
+        <v>0.59424041426712104</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>32</v>
       </c>
@@ -5760,8 +6432,14 @@
       <c r="O112">
         <v>1.92991139</v>
       </c>
-    </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P112">
+        <v>4.6860470000000003</v>
+      </c>
+      <c r="Q112">
+        <v>1.62597430135506</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>32</v>
       </c>
@@ -5807,8 +6485,14 @@
       <c r="O113">
         <v>1.8733360800000001</v>
       </c>
-    </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P113">
+        <v>3.0232559999999999</v>
+      </c>
+      <c r="Q113">
+        <v>0.45051202337744201</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>32</v>
       </c>
@@ -5854,8 +6538,14 @@
       <c r="O114">
         <v>1.27904617</v>
       </c>
-    </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P114">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="Q114">
+        <v>-0.57261195519307595</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>32</v>
       </c>
@@ -5901,8 +6591,14 @@
       <c r="O115">
         <v>1.3826604600000001</v>
       </c>
-    </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P115">
+        <v>3.139535</v>
+      </c>
+      <c r="Q115">
+        <v>0.35762975946984699</v>
+      </c>
+    </row>
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>32</v>
       </c>
@@ -5948,8 +6644,14 @@
       <c r="O116">
         <v>1.5639474600000001</v>
       </c>
-    </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P116">
+        <v>2.232558</v>
+      </c>
+      <c r="Q116">
+        <v>-1.1035662723721</v>
+      </c>
+    </row>
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>32</v>
       </c>
@@ -5995,8 +6697,14 @@
       <c r="O117">
         <v>1.4194650200000001</v>
       </c>
-    </row>
-    <row r="118" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P117">
+        <v>3.4069769999999999</v>
+      </c>
+      <c r="Q117">
+        <v>0.86867982001842003</v>
+      </c>
+    </row>
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>32</v>
       </c>
@@ -6042,8 +6750,14 @@
       <c r="O118">
         <v>1.1651975000000001</v>
       </c>
-    </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P118">
+        <v>2.4767440000000001</v>
+      </c>
+      <c r="Q118">
+        <v>-1.56015161192538</v>
+      </c>
+    </row>
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>32</v>
       </c>
@@ -6089,8 +6803,14 @@
       <c r="O119">
         <v>0.81631741999999996</v>
       </c>
-    </row>
-    <row r="120" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P119">
+        <v>2.139535</v>
+      </c>
+      <c r="Q119">
+        <v>-0.89445723255702703</v>
+      </c>
+    </row>
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>32</v>
       </c>
@@ -6136,8 +6856,14 @@
       <c r="O120">
         <v>1.1062745700000001</v>
       </c>
-    </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P120">
+        <v>3.1744189999999999</v>
+      </c>
+      <c r="Q120">
+        <v>1.2649733888457</v>
+      </c>
+    </row>
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>32</v>
       </c>
@@ -6183,8 +6909,14 @@
       <c r="O121">
         <v>1.77088376</v>
       </c>
-    </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P121">
+        <v>3.0348839999999999</v>
+      </c>
+      <c r="Q121">
+        <v>9.9378862355803094E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>32</v>
       </c>
@@ -6230,8 +6962,14 @@
       <c r="O122">
         <v>2.0660956700000002</v>
       </c>
-    </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P122">
+        <v>3.3488370000000001</v>
+      </c>
+      <c r="Q122">
+        <v>1.13016254368503</v>
+      </c>
+    </row>
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>32</v>
       </c>
@@ -6277,8 +7015,14 @@
       <c r="O123">
         <v>1.5441607399999999</v>
       </c>
-    </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P123">
+        <v>2.1976740000000001</v>
+      </c>
+      <c r="Q123">
+        <v>-1.15957577014644</v>
+      </c>
+    </row>
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>32</v>
       </c>
@@ -6324,8 +7068,14 @@
       <c r="O124">
         <v>1.5604093999999999</v>
       </c>
-    </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P124">
+        <v>2.0697670000000001</v>
+      </c>
+      <c r="Q124">
+        <v>-0.67094339766853195</v>
+      </c>
+    </row>
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>32</v>
       </c>
@@ -6371,8 +7121,14 @@
       <c r="O125">
         <v>0.54231976999999998</v>
       </c>
-    </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P125">
+        <v>2.7093020000000001</v>
+      </c>
+      <c r="Q125">
+        <v>-0.53926567413807602</v>
+      </c>
+    </row>
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>32</v>
       </c>
@@ -6418,8 +7174,14 @@
       <c r="O126">
         <v>0.85273761999999997</v>
       </c>
-    </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P126">
+        <v>3.2093020000000001</v>
+      </c>
+      <c r="Q126">
+        <v>0.10678108407287</v>
+      </c>
+    </row>
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>32</v>
       </c>
@@ -6465,8 +7227,14 @@
       <c r="O127">
         <v>1.6004913199999999</v>
       </c>
-    </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P127">
+        <v>2.104651</v>
+      </c>
+      <c r="Q127">
+        <v>-0.573110681586112</v>
+      </c>
+    </row>
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>32</v>
       </c>
@@ -6512,8 +7280,14 @@
       <c r="O128">
         <v>1.6736028700000001</v>
       </c>
-    </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P128">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q128">
+        <v>1.4253495045725199E-2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>32</v>
       </c>
@@ -6559,8 +7333,14 @@
       <c r="O129">
         <v>1.8899544100000001</v>
       </c>
-    </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P129">
+        <v>4.0813949999999997</v>
+      </c>
+      <c r="Q129">
+        <v>1.3881773607705301</v>
+      </c>
+    </row>
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>32</v>
       </c>
@@ -6606,8 +7386,14 @@
       <c r="O130">
         <v>0.36501940999999999</v>
       </c>
-    </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P130">
+        <v>2.7209300000000001</v>
+      </c>
+      <c r="Q130">
+        <v>-1.17099999461093</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>32</v>
       </c>
@@ -6653,8 +7439,14 @@
       <c r="O131">
         <v>1.1799027099999999</v>
       </c>
-    </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P131">
+        <v>3.9186049999999999</v>
+      </c>
+      <c r="Q131">
+        <v>1.5960348153363799</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>32</v>
       </c>
@@ -6700,8 +7492,14 @@
       <c r="O132">
         <v>1.6014885800000001</v>
       </c>
-    </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P132">
+        <v>2.9186049999999999</v>
+      </c>
+      <c r="Q132">
+        <v>0.27609733374393503</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>32</v>
       </c>
@@ -6747,8 +7545,14 @@
       <c r="O133">
         <v>1.0969308900000001</v>
       </c>
-    </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P133">
+        <v>2.3372090000000001</v>
+      </c>
+      <c r="Q133">
+        <v>-1.0258254984709301</v>
+      </c>
+    </row>
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>32</v>
       </c>
@@ -6794,8 +7598,14 @@
       <c r="O134">
         <v>0.14487807</v>
       </c>
-    </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P134">
+        <v>2.0697670000000001</v>
+      </c>
+      <c r="Q134">
+        <v>-0.52132143467367897</v>
+      </c>
+    </row>
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>32</v>
       </c>
@@ -6841,8 +7651,14 @@
       <c r="O135">
         <v>0.31177881000000002</v>
       </c>
-    </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P135">
+        <v>2.4418600000000001</v>
+      </c>
+      <c r="Q135">
+        <v>-0.65779663793829402</v>
+      </c>
+    </row>
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>32</v>
       </c>
@@ -6888,8 +7704,14 @@
       <c r="O136">
         <v>0.49476659000000001</v>
       </c>
-    </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P136">
+        <v>2.9069769999999999</v>
+      </c>
+      <c r="Q136">
+        <v>-0.15969400955849</v>
+      </c>
+    </row>
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>32</v>
       </c>
@@ -6935,8 +7757,14 @@
       <c r="O137">
         <v>1.7752487299999999</v>
       </c>
-    </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P137">
+        <v>2.8139530000000001</v>
+      </c>
+      <c r="Q137">
+        <v>0.37119205741671901</v>
+      </c>
+    </row>
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>32</v>
       </c>
@@ -6982,8 +7810,14 @@
       <c r="O138">
         <v>1.519593</v>
       </c>
-    </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P138">
+        <v>2.011628</v>
+      </c>
+      <c r="Q138">
+        <v>-1.2176622325858</v>
+      </c>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>32</v>
       </c>
@@ -7029,8 +7863,14 @@
       <c r="O139">
         <v>1.7112386399999999</v>
       </c>
-    </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P139">
+        <v>1.9069769999999999</v>
+      </c>
+      <c r="Q139">
+        <v>0.68435145585984603</v>
+      </c>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>32</v>
       </c>
@@ -7076,8 +7916,14 @@
       <c r="O140">
         <v>0.41092578000000002</v>
       </c>
-    </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P140">
+        <v>1.9069769999999999</v>
+      </c>
+      <c r="Q140">
+        <v>0.64804255221587903</v>
+      </c>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>32</v>
       </c>
@@ -7123,8 +7969,14 @@
       <c r="O141">
         <v>1.43228833</v>
       </c>
-    </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P141">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q141">
+        <v>1.2695725624237699</v>
+      </c>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>32</v>
       </c>
@@ -7170,8 +8022,14 @@
       <c r="O142">
         <v>0.82698716999999999</v>
       </c>
-    </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P142">
+        <v>2.5348839999999999</v>
+      </c>
+      <c r="Q142">
+        <v>0.49157016942829102</v>
+      </c>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>32</v>
       </c>
@@ -7217,8 +8075,14 @@
       <c r="O143">
         <v>0</v>
       </c>
-    </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P143">
+        <v>1</v>
+      </c>
+      <c r="Q143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>32</v>
       </c>
@@ -7264,8 +8128,14 @@
       <c r="O144">
         <v>1.3646575000000001</v>
       </c>
-    </row>
-    <row r="145" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P144">
+        <v>2</v>
+      </c>
+      <c r="Q144">
+        <v>-1.0804638885843499E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>32</v>
       </c>
@@ -7311,8 +8181,14 @@
       <c r="O145">
         <v>0.52168028</v>
       </c>
-    </row>
-    <row r="146" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P145">
+        <v>2.255814</v>
+      </c>
+      <c r="Q145">
+        <v>-1.0898116710568999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>32</v>
       </c>
@@ -7358,8 +8234,14 @@
       <c r="O146">
         <v>0.63604704999999995</v>
       </c>
-    </row>
-    <row r="147" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P146">
+        <v>2.744186</v>
+      </c>
+      <c r="Q146">
+        <v>0.40752162142720699</v>
+      </c>
+    </row>
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>32</v>
       </c>
@@ -7405,8 +8287,14 @@
       <c r="O147">
         <v>1.0636474499999999</v>
       </c>
-    </row>
-    <row r="148" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P147">
+        <v>2.8488370000000001</v>
+      </c>
+      <c r="Q147">
+        <v>0.56636518085877396</v>
+      </c>
+    </row>
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>32</v>
       </c>
@@ -7452,8 +8340,14 @@
       <c r="O148">
         <v>7.1012220000000001E-2</v>
       </c>
-    </row>
-    <row r="149" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P148">
+        <v>1.0465120000000001</v>
+      </c>
+      <c r="Q148">
+        <v>-1.27254005967114</v>
+      </c>
+    </row>
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>32</v>
       </c>
@@ -7499,8 +8393,14 @@
       <c r="O149">
         <v>1.11952995</v>
       </c>
-    </row>
-    <row r="150" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P149">
+        <v>2.0232559999999999</v>
+      </c>
+      <c r="Q149">
+        <v>-0.74234555307836503</v>
+      </c>
+    </row>
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>32</v>
       </c>
@@ -7546,8 +8446,14 @@
       <c r="O150">
         <v>0.14120704000000001</v>
       </c>
-    </row>
-    <row r="151" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P150">
+        <v>1.1511629999999999</v>
+      </c>
+      <c r="Q150">
+        <v>-1.02832603868804</v>
+      </c>
+    </row>
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>32</v>
       </c>
@@ -7593,8 +8499,14 @@
       <c r="O151">
         <v>1.63025771</v>
       </c>
-    </row>
-    <row r="152" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P151">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q151">
+        <v>1.3312180296459699</v>
+      </c>
+    </row>
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>32</v>
       </c>
@@ -7640,8 +8552,14 @@
       <c r="O152">
         <v>2.2585079399999999</v>
       </c>
-    </row>
-    <row r="153" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P152">
+        <v>3.139535</v>
+      </c>
+      <c r="Q152">
+        <v>1.02245517212468</v>
+      </c>
+    </row>
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>32</v>
       </c>
@@ -7687,8 +8605,14 @@
       <c r="O153">
         <v>2.2852496000000002</v>
       </c>
-    </row>
-    <row r="154" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P153">
+        <v>3.2093020000000001</v>
+      </c>
+      <c r="Q153">
+        <v>1.38934110860916</v>
+      </c>
+    </row>
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>35</v>
       </c>
@@ -7734,8 +8658,14 @@
       <c r="O154">
         <v>0.86730971000000001</v>
       </c>
-    </row>
-    <row r="155" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P154">
+        <v>3.2093020000000001</v>
+      </c>
+      <c r="Q154">
+        <v>-0.57894887306381004</v>
+      </c>
+    </row>
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>35</v>
       </c>
@@ -7781,8 +8711,14 @@
       <c r="O155">
         <v>1.60690661</v>
       </c>
-    </row>
-    <row r="156" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P155">
+        <v>4.0465119999999999</v>
+      </c>
+      <c r="Q155">
+        <v>0.27306388122730701</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>35</v>
       </c>
@@ -7828,8 +8764,14 @@
       <c r="O156">
         <v>0.83329427</v>
       </c>
-    </row>
-    <row r="157" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P156">
+        <v>3.872093</v>
+      </c>
+      <c r="Q156">
+        <v>-9.1129006328532491E-3</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>35</v>
       </c>
@@ -7875,8 +8817,14 @@
       <c r="O157">
         <v>1.9389763600000001</v>
       </c>
-    </row>
-    <row r="158" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P157">
+        <v>2.9302329999999999</v>
+      </c>
+      <c r="Q157">
+        <v>-0.344339749027257</v>
+      </c>
+    </row>
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>35</v>
       </c>
@@ -7922,8 +8870,14 @@
       <c r="O158">
         <v>1.48570541</v>
       </c>
-    </row>
-    <row r="159" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P158">
+        <v>3.0813950000000001</v>
+      </c>
+      <c r="Q158">
+        <v>-1.1964147127026601</v>
+      </c>
+    </row>
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>35</v>
       </c>
@@ -7969,8 +8923,14 @@
       <c r="O159">
         <v>2.0236097900000001</v>
       </c>
-    </row>
-    <row r="160" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P159">
+        <v>4.2790699999999999</v>
+      </c>
+      <c r="Q159">
+        <v>1.61543796928862</v>
+      </c>
+    </row>
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>35</v>
       </c>
@@ -8016,8 +8976,14 @@
       <c r="O160">
         <v>1.5328693600000001</v>
       </c>
-    </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P160">
+        <v>2.2790699999999999</v>
+      </c>
+      <c r="Q160">
+        <v>-0.97867283796956706</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>35</v>
       </c>
@@ -8063,8 +9029,14 @@
       <c r="O161">
         <v>1.7654068199999999</v>
       </c>
-    </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P161">
+        <v>3.0465119999999999</v>
+      </c>
+      <c r="Q161">
+        <v>-0.57892962498161005</v>
+      </c>
+    </row>
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>35</v>
       </c>
@@ -8110,8 +9082,14 @@
       <c r="O162">
         <v>1.2010794</v>
       </c>
-    </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P162">
+        <v>3.9302329999999999</v>
+      </c>
+      <c r="Q162">
+        <v>0.41587227535982302</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>35</v>
       </c>
@@ -8157,8 +9135,14 @@
       <c r="O163">
         <v>1.7558158399999999</v>
       </c>
-    </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P163">
+        <v>2.9651160000000001</v>
+      </c>
+      <c r="Q163">
+        <v>-0.35171667658892902</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>35</v>
       </c>
@@ -8204,8 +9188,14 @@
       <c r="O164">
         <v>2.0471740199999999</v>
       </c>
-    </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P164">
+        <v>5.5581399999999999</v>
+      </c>
+      <c r="Q164">
+        <v>1.1189620681885899</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>35</v>
       </c>
@@ -8251,8 +9241,14 @@
       <c r="O165">
         <v>1.9053784899999999</v>
       </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P165">
+        <v>2.9302329999999999</v>
+      </c>
+      <c r="Q165">
+        <v>-0.12043221569332201</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>35</v>
       </c>
@@ -8298,8 +9294,14 @@
       <c r="O166">
         <v>1.83827005</v>
       </c>
-    </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P166">
+        <v>3.2790699999999999</v>
+      </c>
+      <c r="Q166">
+        <v>-1.0086309220616401</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>35</v>
       </c>
@@ -8345,8 +9347,14 @@
       <c r="O167">
         <v>0.33097686999999998</v>
       </c>
-    </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P167">
+        <v>2.8372090000000001</v>
+      </c>
+      <c r="Q167">
+        <v>-0.64233045391593502</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>35</v>
       </c>
@@ -8392,8 +9400,14 @@
       <c r="O168">
         <v>1.1209334</v>
       </c>
-    </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P168">
+        <v>2.767442</v>
+      </c>
+      <c r="Q168">
+        <v>-0.62149177788745302</v>
+      </c>
+    </row>
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>35</v>
       </c>
@@ -8439,8 +9453,14 @@
       <c r="O169">
         <v>1.01588455</v>
       </c>
-    </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P169">
+        <v>3.9534880000000001</v>
+      </c>
+      <c r="Q169">
+        <v>0.83277575673055104</v>
+      </c>
+    </row>
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>35</v>
       </c>
@@ -8486,8 +9506,14 @@
       <c r="O170">
         <v>0.56865379999999999</v>
       </c>
-    </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P170">
+        <v>3.4069769999999999</v>
+      </c>
+      <c r="Q170">
+        <v>-1.0103822874587001</v>
+      </c>
+    </row>
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>35</v>
       </c>
@@ -8533,8 +9559,14 @@
       <c r="O171">
         <v>1.0330321600000001</v>
       </c>
-    </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P171">
+        <v>2.5348839999999999</v>
+      </c>
+      <c r="Q171">
+        <v>0.55657521663754095</v>
+      </c>
+    </row>
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>35</v>
       </c>
@@ -8580,8 +9612,14 @@
       <c r="O172">
         <v>2.2641640000000001</v>
       </c>
-    </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P172">
+        <v>4.6860470000000003</v>
+      </c>
+      <c r="Q172">
+        <v>1.13714773742395</v>
+      </c>
+    </row>
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>35</v>
       </c>
@@ -8627,8 +9665,14 @@
       <c r="O173">
         <v>2.1345999999999998</v>
       </c>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P173">
+        <v>4.8372089999999996</v>
+      </c>
+      <c r="Q173">
+        <v>1.33326773770155</v>
+      </c>
+    </row>
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>35</v>
       </c>
@@ -8674,8 +9718,14 @@
       <c r="O174">
         <v>1.37818186</v>
       </c>
-    </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P174">
+        <v>3.4418600000000001</v>
+      </c>
+      <c r="Q174">
+        <v>0.46545102727544901</v>
+      </c>
+    </row>
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>35</v>
       </c>
@@ -8721,8 +9771,14 @@
       <c r="O175">
         <v>1.2004723500000001</v>
       </c>
-    </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P175">
+        <v>2.9186049999999999</v>
+      </c>
+      <c r="Q175">
+        <v>0.243748841386982</v>
+      </c>
+    </row>
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>35</v>
       </c>
@@ -8768,8 +9824,14 @@
       <c r="O176">
         <v>0.83148363000000003</v>
       </c>
-    </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P176">
+        <v>3.5813950000000001</v>
+      </c>
+      <c r="Q176">
+        <v>0.75123855653351601</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>35</v>
       </c>
@@ -8815,8 +9877,14 @@
       <c r="O177">
         <v>1.4112252199999999</v>
       </c>
-    </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P177">
+        <v>3.9651160000000001</v>
+      </c>
+      <c r="Q177">
+        <v>0.32025903219898</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>35</v>
       </c>
@@ -8862,8 +9930,14 @@
       <c r="O178">
         <v>1.6303742699999999</v>
       </c>
-    </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P178">
+        <v>3.3488370000000001</v>
+      </c>
+      <c r="Q178">
+        <v>-1.2647323436404401</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>35</v>
       </c>
@@ -8909,8 +9983,14 @@
       <c r="O179">
         <v>0.93075169999999996</v>
       </c>
-    </row>
-    <row r="180" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P179">
+        <v>2.2209300000000001</v>
+      </c>
+      <c r="Q179">
+        <v>-1.6208205720461599</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>35</v>
       </c>
@@ -8956,8 +10036,14 @@
       <c r="O180">
         <v>1.5902593700000001</v>
       </c>
-    </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P180">
+        <v>3.244186</v>
+      </c>
+      <c r="Q180">
+        <v>0.85197042020775404</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>35</v>
       </c>
@@ -9003,8 +10089,14 @@
       <c r="O181">
         <v>1.74629378</v>
       </c>
-    </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P181">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q181">
+        <v>-1.0512463334588</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>35</v>
       </c>
@@ -9050,8 +10142,14 @@
       <c r="O182">
         <v>0.58654214999999998</v>
       </c>
-    </row>
-    <row r="183" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P182">
+        <v>3.732558</v>
+      </c>
+      <c r="Q182">
+        <v>0.851848705073047</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>35</v>
       </c>
@@ -9097,8 +10195,14 @@
       <c r="O183">
         <v>1.50589934</v>
       </c>
-    </row>
-    <row r="184" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P183">
+        <v>3.0813950000000001</v>
+      </c>
+      <c r="Q183">
+        <v>-0.825814392301357</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>35</v>
       </c>
@@ -9144,8 +10248,14 @@
       <c r="O184">
         <v>1.8835478699999999</v>
       </c>
-    </row>
-    <row r="185" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P184">
+        <v>3.4767440000000001</v>
+      </c>
+      <c r="Q184">
+        <v>-0.97657568993463895</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>35</v>
       </c>
@@ -9191,8 +10301,14 @@
       <c r="O185">
         <v>1.6301569600000001</v>
       </c>
-    </row>
-    <row r="186" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P185">
+        <v>3.744186</v>
+      </c>
+      <c r="Q185">
+        <v>0.45746509955147502</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>35</v>
       </c>
@@ -9238,8 +10354,14 @@
       <c r="O186">
         <v>1.1027005299999999</v>
       </c>
-    </row>
-    <row r="187" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P186">
+        <v>2.616279</v>
+      </c>
+      <c r="Q186">
+        <v>-1.42653910548955</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>35</v>
       </c>
@@ -9285,8 +10407,14 @@
       <c r="O187">
         <v>0.52356168000000003</v>
       </c>
-    </row>
-    <row r="188" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P187">
+        <v>2.604651</v>
+      </c>
+      <c r="Q187">
+        <v>-1.3166919713757701</v>
+      </c>
+    </row>
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>35</v>
       </c>
@@ -9332,8 +10460,14 @@
       <c r="O188">
         <v>1.24505994</v>
       </c>
-    </row>
-    <row r="189" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P188">
+        <v>2.988372</v>
+      </c>
+      <c r="Q188">
+        <v>-0.63685208389418402</v>
+      </c>
+    </row>
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>35</v>
       </c>
@@ -9379,8 +10513,14 @@
       <c r="O189">
         <v>1.71610303</v>
       </c>
-    </row>
-    <row r="190" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P189">
+        <v>4.9418600000000001</v>
+      </c>
+      <c r="Q189">
+        <v>1.2525482739534699</v>
+      </c>
+    </row>
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>35</v>
       </c>
@@ -9426,8 +10566,14 @@
       <c r="O190">
         <v>0.58464119000000003</v>
       </c>
-    </row>
-    <row r="191" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P190">
+        <v>3.3023259999999999</v>
+      </c>
+      <c r="Q190">
+        <v>-0.40626703283263799</v>
+      </c>
+    </row>
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>35</v>
       </c>
@@ -9473,8 +10619,14 @@
       <c r="O191">
         <v>2.3006363300000001</v>
       </c>
-    </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P191">
+        <v>5</v>
+      </c>
+      <c r="Q191">
+        <v>1.9088537974642099</v>
+      </c>
+    </row>
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>35</v>
       </c>
@@ -9520,8 +10672,14 @@
       <c r="O192">
         <v>1.4288336800000001</v>
       </c>
-    </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P192">
+        <v>3.104651</v>
+      </c>
+      <c r="Q192">
+        <v>-0.13320842596621199</v>
+      </c>
+    </row>
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>35</v>
       </c>
@@ -9567,8 +10725,14 @@
       <c r="O193">
         <v>1.5748640599999999</v>
       </c>
-    </row>
-    <row r="194" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P193">
+        <v>2.5348839999999999</v>
+      </c>
+      <c r="Q193">
+        <v>-0.94970793367153705</v>
+      </c>
+    </row>
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>35</v>
       </c>
@@ -9614,8 +10778,14 @@
       <c r="O194">
         <v>0.90384748999999998</v>
       </c>
-    </row>
-    <row r="195" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P194">
+        <v>2.1744189999999999</v>
+      </c>
+      <c r="Q194">
+        <v>-0.385795275079928</v>
+      </c>
+    </row>
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>35</v>
       </c>
@@ -9661,8 +10831,14 @@
       <c r="O195">
         <v>0.69839001999999994</v>
       </c>
-    </row>
-    <row r="196" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P195">
+        <v>3.6976740000000001</v>
+      </c>
+      <c r="Q195">
+        <v>0.33469085787095199</v>
+      </c>
+    </row>
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>35</v>
       </c>
@@ -9708,8 +10884,14 @@
       <c r="O196">
         <v>1.41621587</v>
       </c>
-    </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P196">
+        <v>4.0697669999999997</v>
+      </c>
+      <c r="Q196">
+        <v>0.90522851569042295</v>
+      </c>
+    </row>
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>35</v>
       </c>
@@ -9755,8 +10937,14 @@
       <c r="O197">
         <v>1.76444801</v>
       </c>
-    </row>
-    <row r="198" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P197">
+        <v>3.5232559999999999</v>
+      </c>
+      <c r="Q197">
+        <v>0.57079105752061898</v>
+      </c>
+    </row>
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>35</v>
       </c>
@@ -9802,8 +10990,14 @@
       <c r="O198">
         <v>1.3124489500000001</v>
       </c>
-    </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P198">
+        <v>2.4302329999999999</v>
+      </c>
+      <c r="Q198">
+        <v>-1.6003784042034599</v>
+      </c>
+    </row>
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>35</v>
       </c>
@@ -9849,8 +11043,14 @@
       <c r="O199">
         <v>1.4070476000000001</v>
       </c>
-    </row>
-    <row r="200" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P199">
+        <v>2.3139530000000001</v>
+      </c>
+      <c r="Q199">
+        <v>-0.98197638646284202</v>
+      </c>
+    </row>
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>35</v>
       </c>
@@ -9896,8 +11096,14 @@
       <c r="O200">
         <v>0.96146220999999998</v>
       </c>
-    </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P200">
+        <v>2.244186</v>
+      </c>
+      <c r="Q200">
+        <v>-0.17343248915925399</v>
+      </c>
+    </row>
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>35</v>
       </c>
@@ -9943,8 +11149,14 @@
       <c r="O201">
         <v>1.6464895500000001</v>
       </c>
-    </row>
-    <row r="202" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P201">
+        <v>3.0465119999999999</v>
+      </c>
+      <c r="Q201">
+        <v>7.8168597310298293E-2</v>
+      </c>
+    </row>
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>35</v>
       </c>
@@ -9990,8 +11202,14 @@
       <c r="O202">
         <v>1.6887400299999999</v>
       </c>
-    </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P202">
+        <v>3.7790699999999999</v>
+      </c>
+      <c r="Q202">
+        <v>0.277824778521087</v>
+      </c>
+    </row>
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>35</v>
       </c>
@@ -10037,8 +11255,14 @@
       <c r="O203">
         <v>1.0778233800000001</v>
       </c>
-    </row>
-    <row r="204" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P203">
+        <v>2.6744189999999999</v>
+      </c>
+      <c r="Q203">
+        <v>-0.622342901843426</v>
+      </c>
+    </row>
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>35</v>
       </c>
@@ -10084,8 +11308,14 @@
       <c r="O204">
         <v>1.8752500999999999</v>
       </c>
-    </row>
-    <row r="205" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P204">
+        <v>4</v>
+      </c>
+      <c r="Q204">
+        <v>0.92886253814081998</v>
+      </c>
+    </row>
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>35</v>
       </c>
@@ -10131,8 +11361,14 @@
       <c r="O205">
         <v>1.2076200800000001</v>
       </c>
-    </row>
-    <row r="206" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P205">
+        <v>2.2906979999999999</v>
+      </c>
+      <c r="Q205">
+        <v>-0.92753952605829304</v>
+      </c>
+    </row>
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>35</v>
       </c>
@@ -10178,8 +11414,14 @@
       <c r="O206">
         <v>0.64633335000000003</v>
       </c>
-    </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P206">
+        <v>3.104651</v>
+      </c>
+      <c r="Q206">
+        <v>-0.66913983728557702</v>
+      </c>
+    </row>
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>35</v>
       </c>
@@ -10225,8 +11467,14 @@
       <c r="O207">
         <v>1.1203483700000001</v>
       </c>
-    </row>
-    <row r="208" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P207">
+        <v>2.9186049999999999</v>
+      </c>
+      <c r="Q207">
+        <v>-0.13301655758656</v>
+      </c>
+    </row>
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>35</v>
       </c>
@@ -10272,8 +11520,14 @@
       <c r="O208">
         <v>1.0895326599999999</v>
       </c>
-    </row>
-    <row r="209" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P208">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="Q208">
+        <v>-0.59154497138401996</v>
+      </c>
+    </row>
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>35</v>
       </c>
@@ -10319,8 +11573,14 @@
       <c r="O209">
         <v>1.51029795</v>
       </c>
-    </row>
-    <row r="210" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P209">
+        <v>3.604651</v>
+      </c>
+      <c r="Q209">
+        <v>0.47892308047495902</v>
+      </c>
+    </row>
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>35</v>
       </c>
@@ -10366,8 +11626,14 @@
       <c r="O210">
         <v>0.48405532000000001</v>
       </c>
-    </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P210">
+        <v>2.5348839999999999</v>
+      </c>
+      <c r="Q210">
+        <v>-0.82137450514955002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>35</v>
       </c>
@@ -10413,8 +11679,14 @@
       <c r="O211">
         <v>0.58531648000000003</v>
       </c>
-    </row>
-    <row r="212" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P211">
+        <v>2.1627909999999999</v>
+      </c>
+      <c r="Q211">
+        <v>-0.72522105085269695</v>
+      </c>
+    </row>
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>35</v>
       </c>
@@ -10460,8 +11732,14 @@
       <c r="O212">
         <v>0.98923903000000002</v>
       </c>
-    </row>
-    <row r="213" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P212">
+        <v>3.1627909999999999</v>
+      </c>
+      <c r="Q212">
+        <v>-0.69372879366846196</v>
+      </c>
+    </row>
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>35</v>
       </c>
@@ -10507,8 +11785,14 @@
       <c r="O213">
         <v>1.5508414399999999</v>
       </c>
-    </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P213">
+        <v>2.4418600000000001</v>
+      </c>
+      <c r="Q213">
+        <v>-0.71211506401049196</v>
+      </c>
+    </row>
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>35</v>
       </c>
@@ -10554,8 +11838,14 @@
       <c r="O214">
         <v>0.84765988999999997</v>
       </c>
-    </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P214">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q214">
+        <v>9.8025688365240504E-2</v>
+      </c>
+    </row>
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>35</v>
       </c>
@@ -10601,8 +11891,14 @@
       <c r="O215">
         <v>0.15788938</v>
       </c>
-    </row>
-    <row r="216" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P215">
+        <v>2.1744189999999999</v>
+      </c>
+      <c r="Q215">
+        <v>-0.30002712228997303</v>
+      </c>
+    </row>
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>35</v>
       </c>
@@ -10648,8 +11944,14 @@
       <c r="O216">
         <v>0.39497658000000002</v>
       </c>
-    </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P216">
+        <v>2.6627909999999999</v>
+      </c>
+      <c r="Q216">
+        <v>-0.29670392566109099</v>
+      </c>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>35</v>
       </c>
@@ -10695,8 +11997,14 @@
       <c r="O217">
         <v>0.98265309999999995</v>
       </c>
-    </row>
-    <row r="218" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P217">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q217">
+        <v>1.2934877951552199</v>
+      </c>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>35</v>
       </c>
@@ -10742,8 +12050,14 @@
       <c r="O218">
         <v>1.04816278</v>
       </c>
-    </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P218">
+        <v>2.5</v>
+      </c>
+      <c r="Q218">
+        <v>0.36494051352248003</v>
+      </c>
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>35</v>
       </c>
@@ -10789,8 +12103,14 @@
       <c r="O219">
         <v>1.42492686</v>
       </c>
-    </row>
-    <row r="220" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P219">
+        <v>1.9069769999999999</v>
+      </c>
+      <c r="Q219">
+        <v>0.73074179298280595</v>
+      </c>
+    </row>
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>35</v>
       </c>
@@ -10836,8 +12156,14 @@
       <c r="O220">
         <v>0.62439445999999998</v>
       </c>
-    </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P220">
+        <v>1.0930230000000001</v>
+      </c>
+      <c r="Q220">
+        <v>-1.9983224217228199</v>
+      </c>
+    </row>
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>35</v>
       </c>
@@ -10883,8 +12209,14 @@
       <c r="O221">
         <v>1.4062978900000001</v>
       </c>
-    </row>
-    <row r="222" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P221">
+        <v>2.6627909999999999</v>
+      </c>
+      <c r="Q221">
+        <v>0.76767631728040997</v>
+      </c>
+    </row>
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>35</v>
       </c>
@@ -10930,8 +12262,14 @@
       <c r="O222">
         <v>0.49208987999999998</v>
       </c>
-    </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P222">
+        <v>2.627907</v>
+      </c>
+      <c r="Q222">
+        <v>2.9429829401030401E-2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>35</v>
       </c>
@@ -10977,8 +12315,14 @@
       <c r="O223">
         <v>1.6662835499999999</v>
       </c>
-    </row>
-    <row r="224" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P223">
+        <v>2.4767440000000001</v>
+      </c>
+      <c r="Q223">
+        <v>0.38142214659985302</v>
+      </c>
+    </row>
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>35</v>
       </c>
@@ -11024,8 +12368,14 @@
       <c r="O224">
         <v>1.6436659300000001</v>
       </c>
-    </row>
-    <row r="225" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P224">
+        <v>2.1511629999999999</v>
+      </c>
+      <c r="Q224">
+        <v>-0.38524796702328901</v>
+      </c>
+    </row>
+    <row r="225" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>35</v>
       </c>
@@ -11071,8 +12421,14 @@
       <c r="O225">
         <v>0.37794952999999998</v>
       </c>
-    </row>
-    <row r="226" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P225">
+        <v>2.104651</v>
+      </c>
+      <c r="Q225">
+        <v>-0.98674941478417799</v>
+      </c>
+    </row>
+    <row r="226" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>35</v>
       </c>
@@ -11118,8 +12474,14 @@
       <c r="O226">
         <v>0.37769593000000001</v>
       </c>
-    </row>
-    <row r="227" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P226">
+        <v>2.895349</v>
+      </c>
+      <c r="Q226">
+        <v>0.22205415803338599</v>
+      </c>
+    </row>
+    <row r="227" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>35</v>
       </c>
@@ -11165,8 +12527,14 @@
       <c r="O227">
         <v>0</v>
       </c>
-    </row>
-    <row r="228" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P227">
+        <v>1</v>
+      </c>
+      <c r="Q227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>35</v>
       </c>
@@ -11212,8 +12580,14 @@
       <c r="O228">
         <v>0.36783484</v>
       </c>
-    </row>
-    <row r="229" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P228">
+        <v>1.9069769999999999</v>
+      </c>
+      <c r="Q228">
+        <v>0.721983362077247</v>
+      </c>
+    </row>
+    <row r="229" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>35</v>
       </c>
@@ -11259,8 +12633,14 @@
       <c r="O229">
         <v>1.6676744699999999</v>
       </c>
-    </row>
-    <row r="230" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P229">
+        <v>3.244186</v>
+      </c>
+      <c r="Q229">
+        <v>0.54547700736354299</v>
+      </c>
+    </row>
+    <row r="230" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>35</v>
       </c>
@@ -11306,8 +12686,14 @@
       <c r="O230">
         <v>0.43751171999999999</v>
       </c>
-    </row>
-    <row r="231" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P230">
+        <v>1.9069769999999999</v>
+      </c>
+      <c r="Q230">
+        <v>0.80027673452701897</v>
+      </c>
+    </row>
+    <row r="231" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>35</v>
       </c>
@@ -11353,8 +12739,14 @@
       <c r="O231">
         <v>2.0175737699999998</v>
       </c>
-    </row>
-    <row r="232" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P231">
+        <v>3.5</v>
+      </c>
+      <c r="Q231">
+        <v>0.87213895931108498</v>
+      </c>
+    </row>
+    <row r="232" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>35</v>
       </c>
@@ -11400,8 +12792,14 @@
       <c r="O232">
         <v>0.82419872999999999</v>
       </c>
-    </row>
-    <row r="233" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P232">
+        <v>2.5697670000000001</v>
+      </c>
+      <c r="Q232">
+        <v>-4.6576482230017098E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>35</v>
       </c>
@@ -11447,8 +12845,14 @@
       <c r="O233">
         <v>2.1519200000000001</v>
       </c>
-    </row>
-    <row r="234" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P233">
+        <v>2.0581399999999999</v>
+      </c>
+      <c r="Q233">
+        <v>8.30493891049741E-2</v>
+      </c>
+    </row>
+    <row r="234" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>36</v>
       </c>
@@ -11494,8 +12898,14 @@
       <c r="O234">
         <v>2.1141286699999999</v>
       </c>
-    </row>
-    <row r="235" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P234">
+        <v>3.7790699999999999</v>
+      </c>
+      <c r="Q234">
+        <v>-0.14649480275693499</v>
+      </c>
+    </row>
+    <row r="235" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>36</v>
       </c>
@@ -11541,8 +12951,14 @@
       <c r="O235">
         <v>2.2369543200000002</v>
       </c>
-    </row>
-    <row r="236" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P235">
+        <v>3.3488370000000001</v>
+      </c>
+      <c r="Q235">
+        <v>-1.0650947816087399</v>
+      </c>
+    </row>
+    <row r="236" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>36</v>
       </c>
@@ -11588,8 +13004,14 @@
       <c r="O236">
         <v>2.05301811</v>
       </c>
-    </row>
-    <row r="237" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P236">
+        <v>3.5813950000000001</v>
+      </c>
+      <c r="Q236">
+        <v>-0.19355605337184001</v>
+      </c>
+    </row>
+    <row r="237" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>36</v>
       </c>
@@ -11635,8 +13057,14 @@
       <c r="O237">
         <v>1.8262086900000001</v>
       </c>
-    </row>
-    <row r="238" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P237">
+        <v>2.8372090000000001</v>
+      </c>
+      <c r="Q237">
+        <v>-1.4350346852826401</v>
+      </c>
+    </row>
+    <row r="238" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>36</v>
       </c>
@@ -11682,8 +13110,14 @@
       <c r="O238">
         <v>1.64261977</v>
       </c>
-    </row>
-    <row r="239" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P238">
+        <v>2.1744189999999999</v>
+      </c>
+      <c r="Q238">
+        <v>-2.7742032681110498</v>
+      </c>
+    </row>
+    <row r="239" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>36</v>
       </c>
@@ -11729,8 +13163,14 @@
       <c r="O239">
         <v>2.20932241</v>
       </c>
-    </row>
-    <row r="240" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P239">
+        <v>3.7790699999999999</v>
+      </c>
+      <c r="Q239">
+        <v>1.5900493845138799</v>
+      </c>
+    </row>
+    <row r="240" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>36</v>
       </c>
@@ -11776,8 +13216,14 @@
       <c r="O240">
         <v>0</v>
       </c>
-    </row>
-    <row r="241" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P240">
+        <v>1</v>
+      </c>
+      <c r="Q240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>36</v>
       </c>
@@ -11823,8 +13269,14 @@
       <c r="O241">
         <v>2.1213674</v>
       </c>
-    </row>
-    <row r="242" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P241">
+        <v>4.9651160000000001</v>
+      </c>
+      <c r="Q241">
+        <v>1.3175204298832299</v>
+      </c>
+    </row>
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>36</v>
       </c>
@@ -11870,8 +13322,14 @@
       <c r="O242">
         <v>0.74695884000000001</v>
       </c>
-    </row>
-    <row r="243" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P242">
+        <v>5.0232559999999999</v>
+      </c>
+      <c r="Q242">
+        <v>1.4329665450117799</v>
+      </c>
+    </row>
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>36</v>
       </c>
@@ -11917,8 +13375,14 @@
       <c r="O243">
         <v>1.45791125</v>
       </c>
-    </row>
-    <row r="244" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P243">
+        <v>3.0348839999999999</v>
+      </c>
+      <c r="Q243">
+        <v>-0.481377080643696</v>
+      </c>
+    </row>
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>36</v>
       </c>
@@ -11964,8 +13428,14 @@
       <c r="O244">
         <v>1.6293114500000001</v>
       </c>
-    </row>
-    <row r="245" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P244">
+        <v>3.767442</v>
+      </c>
+      <c r="Q244">
+        <v>-5.9739118067786597E-3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>36</v>
       </c>
@@ -12011,8 +13481,14 @@
       <c r="O245">
         <v>1.7493881</v>
       </c>
-    </row>
-    <row r="246" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P245">
+        <v>3.4651160000000001</v>
+      </c>
+      <c r="Q245">
+        <v>-4.3905539325780001E-2</v>
+      </c>
+    </row>
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>36</v>
       </c>
@@ -12058,8 +13534,14 @@
       <c r="O246">
         <v>1.66782169</v>
       </c>
-    </row>
-    <row r="247" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P246">
+        <v>2.860465</v>
+      </c>
+      <c r="Q246">
+        <v>-0.61685908884894003</v>
+      </c>
+    </row>
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>36</v>
       </c>
@@ -12105,8 +13587,14 @@
       <c r="O247">
         <v>0.71673606999999995</v>
       </c>
-    </row>
-    <row r="248" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P247">
+        <v>2.3255810000000001</v>
+      </c>
+      <c r="Q247">
+        <v>-1.6484253113602301</v>
+      </c>
+    </row>
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>36</v>
       </c>
@@ -12152,8 +13640,14 @@
       <c r="O248">
         <v>1.7602946100000001</v>
       </c>
-    </row>
-    <row r="249" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P248">
+        <v>3.1627909999999999</v>
+      </c>
+      <c r="Q248">
+        <v>0.30572402430144502</v>
+      </c>
+    </row>
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>36</v>
       </c>
@@ -12199,8 +13693,14 @@
       <c r="O249">
         <v>0.76073681999999998</v>
       </c>
-    </row>
-    <row r="250" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P249">
+        <v>3.9767440000000001</v>
+      </c>
+      <c r="Q249">
+        <v>0.565240659551286</v>
+      </c>
+    </row>
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>36</v>
       </c>
@@ -12246,8 +13746,14 @@
       <c r="O250">
         <v>0.68150979</v>
       </c>
-    </row>
-    <row r="251" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P250">
+        <v>3.0813950000000001</v>
+      </c>
+      <c r="Q250">
+        <v>-0.92253115744963698</v>
+      </c>
+    </row>
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>36</v>
       </c>
@@ -12293,8 +13799,14 @@
       <c r="O251">
         <v>1.84264709</v>
       </c>
-    </row>
-    <row r="252" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P251">
+        <v>5.3139529999999997</v>
+      </c>
+      <c r="Q251">
+        <v>1.20710726486533</v>
+      </c>
+    </row>
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>36</v>
       </c>
@@ -12340,8 +13852,14 @@
       <c r="O252">
         <v>1.8085070599999999</v>
       </c>
-    </row>
-    <row r="253" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P252">
+        <v>3.9186049999999999</v>
+      </c>
+      <c r="Q252">
+        <v>0.55493723344509505</v>
+      </c>
+    </row>
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>36</v>
       </c>
@@ -12387,8 +13905,14 @@
       <c r="O253">
         <v>1.3669289499999999</v>
       </c>
-    </row>
-    <row r="254" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P253">
+        <v>3.9302329999999999</v>
+      </c>
+      <c r="Q253">
+        <v>-0.17386222666308601</v>
+      </c>
+    </row>
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>36</v>
       </c>
@@ -12434,8 +13958,14 @@
       <c r="O254">
         <v>0.72210293999999997</v>
       </c>
-    </row>
-    <row r="255" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P254">
+        <v>3.4302329999999999</v>
+      </c>
+      <c r="Q254">
+        <v>0.48377138120454299</v>
+      </c>
+    </row>
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>36</v>
       </c>
@@ -12481,8 +14011,14 @@
       <c r="O255">
         <v>0.52844347999999997</v>
       </c>
-    </row>
-    <row r="256" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P255">
+        <v>3.8255810000000001</v>
+      </c>
+      <c r="Q255">
+        <v>4.7281411615826302E-2</v>
+      </c>
+    </row>
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>36</v>
       </c>
@@ -12528,8 +14064,14 @@
       <c r="O256">
         <v>1.8910069300000001</v>
       </c>
-    </row>
-    <row r="257" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P256">
+        <v>4.5581399999999999</v>
+      </c>
+      <c r="Q256">
+        <v>-4.37521193960951E-2</v>
+      </c>
+    </row>
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>36</v>
       </c>
@@ -12575,8 +14117,14 @@
       <c r="O257">
         <v>1.8755406800000001</v>
       </c>
-    </row>
-    <row r="258" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P257">
+        <v>3.7093020000000001</v>
+      </c>
+      <c r="Q257">
+        <v>-1.05975258242498</v>
+      </c>
+    </row>
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>36</v>
       </c>
@@ -12622,8 +14170,14 @@
       <c r="O258">
         <v>1.2358966600000001</v>
       </c>
-    </row>
-    <row r="259" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P258">
+        <v>2.8023259999999999</v>
+      </c>
+      <c r="Q258">
+        <v>-1.4936771351995199</v>
+      </c>
+    </row>
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>36</v>
       </c>
@@ -12669,8 +14223,14 @@
       <c r="O259">
         <v>1.69644025</v>
       </c>
-    </row>
-    <row r="260" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P259">
+        <v>3.9767440000000001</v>
+      </c>
+      <c r="Q259">
+        <v>0.19633274230491299</v>
+      </c>
+    </row>
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>36</v>
       </c>
@@ -12716,8 +14276,14 @@
       <c r="O260">
         <v>0.81616781000000005</v>
       </c>
-    </row>
-    <row r="261" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P260">
+        <v>4.2209300000000001</v>
+      </c>
+      <c r="Q260">
+        <v>0.66992909023194103</v>
+      </c>
+    </row>
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>36</v>
       </c>
@@ -12763,8 +14329,14 @@
       <c r="O261">
         <v>1.6202567299999999</v>
       </c>
-    </row>
-    <row r="262" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P261">
+        <v>3.3488370000000001</v>
+      </c>
+      <c r="Q261">
+        <v>-0.87061102971339399</v>
+      </c>
+    </row>
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>36</v>
       </c>
@@ -12810,8 +14382,14 @@
       <c r="O262">
         <v>1.75381776</v>
       </c>
-    </row>
-    <row r="263" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P262">
+        <v>5.6860470000000003</v>
+      </c>
+      <c r="Q262">
+        <v>1.33026940660584</v>
+      </c>
+    </row>
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>36</v>
       </c>
@@ -12857,8 +14435,14 @@
       <c r="O263">
         <v>1.6297378</v>
       </c>
-    </row>
-    <row r="264" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P263">
+        <v>2.511628</v>
+      </c>
+      <c r="Q263">
+        <v>-0.75525191742291797</v>
+      </c>
+    </row>
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>36</v>
       </c>
@@ -12904,8 +14488,14 @@
       <c r="O264">
         <v>1.49705244</v>
       </c>
-    </row>
-    <row r="265" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P264">
+        <v>3.5581399999999999</v>
+      </c>
+      <c r="Q264">
+        <v>-0.64020012624522604</v>
+      </c>
+    </row>
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>36</v>
       </c>
@@ -12951,8 +14541,14 @@
       <c r="O265">
         <v>0.51699410000000001</v>
       </c>
-    </row>
-    <row r="266" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P265">
+        <v>2.511628</v>
+      </c>
+      <c r="Q265">
+        <v>-1.24622807062215</v>
+      </c>
+    </row>
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>36</v>
       </c>
@@ -12998,8 +14594,14 @@
       <c r="O266">
         <v>1.3854505399999999</v>
       </c>
-    </row>
-    <row r="267" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P266">
+        <v>3.9767440000000001</v>
+      </c>
+      <c r="Q266">
+        <v>0.34357526812982098</v>
+      </c>
+    </row>
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>36</v>
       </c>
@@ -13045,8 +14647,14 @@
       <c r="O267">
         <v>1.76067755</v>
       </c>
-    </row>
-    <row r="268" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P267">
+        <v>4.3488369999999996</v>
+      </c>
+      <c r="Q267">
+        <v>1.2366812879343401</v>
+      </c>
+    </row>
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>36</v>
       </c>
@@ -13092,8 +14700,14 @@
       <c r="O268">
         <v>0.66582105000000003</v>
       </c>
-    </row>
-    <row r="269" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P268">
+        <v>3.011628</v>
+      </c>
+      <c r="Q268">
+        <v>-0.78652141925132302</v>
+      </c>
+    </row>
+    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>36</v>
       </c>
@@ -13139,8 +14753,14 @@
       <c r="O269">
         <v>1.9046454900000001</v>
       </c>
-    </row>
-    <row r="270" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P269">
+        <v>3.8255810000000001</v>
+      </c>
+      <c r="Q269">
+        <v>2.31228838936554E-2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>36</v>
       </c>
@@ -13186,8 +14806,14 @@
       <c r="O270">
         <v>0.81487191000000003</v>
       </c>
-    </row>
-    <row r="271" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P270">
+        <v>3.6860469999999999</v>
+      </c>
+      <c r="Q270">
+        <v>1.0282555940445399E-2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>36</v>
       </c>
@@ -13233,8 +14859,14 @@
       <c r="O271">
         <v>1.5249822500000001</v>
       </c>
-    </row>
-    <row r="272" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P271">
+        <v>2.9651160000000001</v>
+      </c>
+      <c r="Q271">
+        <v>-7.7225529098928603E-2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>36</v>
       </c>
@@ -13280,8 +14912,14 @@
       <c r="O272">
         <v>0.41523199999999999</v>
       </c>
-    </row>
-    <row r="273" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P272">
+        <v>2.4418600000000001</v>
+      </c>
+      <c r="Q272">
+        <v>-0.81098131278594698</v>
+      </c>
+    </row>
+    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>36</v>
       </c>
@@ -13327,8 +14965,14 @@
       <c r="O273">
         <v>0.55310408</v>
       </c>
-    </row>
-    <row r="274" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P273">
+        <v>2.2790699999999999</v>
+      </c>
+      <c r="Q273">
+        <v>-1.1414569423074199</v>
+      </c>
+    </row>
+    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>36</v>
       </c>
@@ -13374,8 +15018,14 @@
       <c r="O274">
         <v>0.84443126999999996</v>
       </c>
-    </row>
-    <row r="275" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P274">
+        <v>2.5465119999999999</v>
+      </c>
+      <c r="Q274">
+        <v>-1.47732113205439</v>
+      </c>
+    </row>
+    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>36</v>
       </c>
@@ -13421,8 +15071,14 @@
       <c r="O275">
         <v>1.16060662</v>
       </c>
-    </row>
-    <row r="276" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P275">
+        <v>3.5</v>
+      </c>
+      <c r="Q275">
+        <v>-0.218193601515664</v>
+      </c>
+    </row>
+    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>36</v>
       </c>
@@ -13468,8 +15124,14 @@
       <c r="O276">
         <v>1.4204147</v>
       </c>
-    </row>
-    <row r="277" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P276">
+        <v>2.860465</v>
+      </c>
+      <c r="Q276">
+        <v>-0.61821549465236503</v>
+      </c>
+    </row>
+    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>36</v>
       </c>
@@ -13515,8 +15177,14 @@
       <c r="O277">
         <v>1.3915497699999999</v>
       </c>
-    </row>
-    <row r="278" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P277">
+        <v>3.0465119999999999</v>
+      </c>
+      <c r="Q277">
+        <v>0.12235719025955399</v>
+      </c>
+    </row>
+    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>36</v>
       </c>
@@ -13562,8 +15230,14 @@
       <c r="O278">
         <v>1.5262344299999999</v>
       </c>
-    </row>
-    <row r="279" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P278">
+        <v>3.732558</v>
+      </c>
+      <c r="Q278">
+        <v>0.68792821546608496</v>
+      </c>
+    </row>
+    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>36</v>
       </c>
@@ -13609,8 +15283,14 @@
       <c r="O279">
         <v>1.4656672500000001</v>
       </c>
-    </row>
-    <row r="280" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P279">
+        <v>2.7093020000000001</v>
+      </c>
+      <c r="Q279">
+        <v>-0.65338078468099603</v>
+      </c>
+    </row>
+    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>36</v>
       </c>
@@ -13656,8 +15336,14 @@
       <c r="O280">
         <v>1.7139296399999999</v>
       </c>
-    </row>
-    <row r="281" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P280">
+        <v>2.6860469999999999</v>
+      </c>
+      <c r="Q280">
+        <v>-1.0947416561909</v>
+      </c>
+    </row>
+    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>36</v>
       </c>
@@ -13703,8 +15389,14 @@
       <c r="O281">
         <v>0.55039066999999997</v>
       </c>
-    </row>
-    <row r="282" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P281">
+        <v>2.5348839999999999</v>
+      </c>
+      <c r="Q281">
+        <v>-1.0940612647633801</v>
+      </c>
+    </row>
+    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>36</v>
       </c>
@@ -13750,8 +15442,14 @@
       <c r="O282">
         <v>0.65040050000000005</v>
       </c>
-    </row>
-    <row r="283" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P282">
+        <v>3.4186049999999999</v>
+      </c>
+      <c r="Q282">
+        <v>-0.36007654458655403</v>
+      </c>
+    </row>
+    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>36</v>
       </c>
@@ -13797,8 +15495,14 @@
       <c r="O283">
         <v>0.15903308999999999</v>
       </c>
-    </row>
-    <row r="284" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P283">
+        <v>1.267442</v>
+      </c>
+      <c r="Q283">
+        <v>-1.4732289421087299</v>
+      </c>
+    </row>
+    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>36</v>
       </c>
@@ -13844,8 +15548,14 @@
       <c r="O284">
         <v>1.6170908900000001</v>
       </c>
-    </row>
-    <row r="285" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P284">
+        <v>2.6511629999999999</v>
+      </c>
+      <c r="Q284">
+        <v>0.19715704631928599</v>
+      </c>
+    </row>
+    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>36</v>
       </c>
@@ -13891,8 +15601,14 @@
       <c r="O285">
         <v>1.88226413</v>
       </c>
-    </row>
-    <row r="286" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P285">
+        <v>4.1046509999999996</v>
+      </c>
+      <c r="Q285">
+        <v>1.1227810810148899</v>
+      </c>
+    </row>
+    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>36</v>
       </c>
@@ -13938,8 +15654,14 @@
       <c r="O286">
         <v>0.63283180000000006</v>
       </c>
-    </row>
-    <row r="287" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P286">
+        <v>2.9302329999999999</v>
+      </c>
+      <c r="Q286">
+        <v>-8.1692561692826099E-2</v>
+      </c>
+    </row>
+    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>36</v>
       </c>
@@ -13985,8 +15707,14 @@
       <c r="O287">
         <v>0.74849631000000005</v>
       </c>
-    </row>
-    <row r="288" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P287">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q287">
+        <v>1.2778967861044499</v>
+      </c>
+    </row>
+    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>36</v>
       </c>
@@ -14032,8 +15760,14 @@
       <c r="O288">
         <v>1.00131397</v>
       </c>
-    </row>
-    <row r="289" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P288">
+        <v>3.9302329999999999</v>
+      </c>
+      <c r="Q288">
+        <v>0.49562356851640599</v>
+      </c>
+    </row>
+    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>36</v>
       </c>
@@ -14079,8 +15813,14 @@
       <c r="O289">
         <v>1.3641925800000001</v>
       </c>
-    </row>
-    <row r="290" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P289">
+        <v>2.5813950000000001</v>
+      </c>
+      <c r="Q289">
+        <v>-0.77255326682828895</v>
+      </c>
+    </row>
+    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>36</v>
       </c>
@@ -14126,8 +15866,14 @@
       <c r="O290">
         <v>0.57296533999999999</v>
       </c>
-    </row>
-    <row r="291" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P290">
+        <v>2.4767440000000001</v>
+      </c>
+      <c r="Q290">
+        <v>-1.0174519936389601</v>
+      </c>
+    </row>
+    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>36</v>
       </c>
@@ -14173,8 +15919,14 @@
       <c r="O291">
         <v>0.19956979999999999</v>
       </c>
-    </row>
-    <row r="292" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P291">
+        <v>2.395349</v>
+      </c>
+      <c r="Q291">
+        <v>-1.58427477924277</v>
+      </c>
+    </row>
+    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>36</v>
       </c>
@@ -14220,8 +15972,14 @@
       <c r="O292">
         <v>0</v>
       </c>
-    </row>
-    <row r="293" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P292">
+        <v>1</v>
+      </c>
+      <c r="Q292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>36</v>
       </c>
@@ -14267,8 +16025,14 @@
       <c r="O293">
         <v>0.83510614000000005</v>
       </c>
-    </row>
-    <row r="294" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P293">
+        <v>3.0697670000000001</v>
+      </c>
+      <c r="Q293">
+        <v>1.1021532661334801</v>
+      </c>
+    </row>
+    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>36</v>
       </c>
@@ -14314,8 +16078,14 @@
       <c r="O294">
         <v>1.32217183</v>
       </c>
-    </row>
-    <row r="295" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P294">
+        <v>2.0697670000000001</v>
+      </c>
+      <c r="Q294">
+        <v>-0.68954922581153599</v>
+      </c>
+    </row>
+    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>36</v>
       </c>
@@ -14361,8 +16131,14 @@
       <c r="O295">
         <v>0.28813984999999998</v>
       </c>
-    </row>
-    <row r="296" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P295">
+        <v>1.0697669999999999</v>
+      </c>
+      <c r="Q295">
+        <v>-1.10846199699338</v>
+      </c>
+    </row>
+    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>36</v>
       </c>
@@ -14408,8 +16184,14 @@
       <c r="O296">
         <v>0</v>
       </c>
-    </row>
-    <row r="297" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P296">
+        <v>1</v>
+      </c>
+      <c r="Q296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>36</v>
       </c>
@@ -14455,8 +16237,14 @@
       <c r="O297">
         <v>1.58352176</v>
       </c>
-    </row>
-    <row r="298" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P297">
+        <v>2.104651</v>
+      </c>
+      <c r="Q297">
+        <v>-1.2984169575769799</v>
+      </c>
+    </row>
+    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>36</v>
       </c>
@@ -14502,8 +16290,14 @@
       <c r="O298">
         <v>8.8672899999999999E-3</v>
       </c>
-    </row>
-    <row r="299" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P298">
+        <v>1.116279</v>
+      </c>
+      <c r="Q298">
+        <v>-1.1835916048269199</v>
+      </c>
+    </row>
+    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>36</v>
       </c>
@@ -14549,8 +16343,14 @@
       <c r="O299">
         <v>1.6319130000000001E-2</v>
       </c>
-    </row>
-    <row r="300" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P299">
+        <v>1.1627909999999999</v>
+      </c>
+      <c r="Q299">
+        <v>-1.7394196591793101</v>
+      </c>
+    </row>
+    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>36</v>
       </c>
@@ -14596,8 +16396,14 @@
       <c r="O300">
         <v>0.22093525</v>
       </c>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P300">
+        <v>2.767442</v>
+      </c>
+      <c r="Q300">
+        <v>0.48833561351632199</v>
+      </c>
+    </row>
+    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>36</v>
       </c>
@@ -14643,8 +16449,14 @@
       <c r="O301">
         <v>0</v>
       </c>
-    </row>
-    <row r="302" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P301">
+        <v>1</v>
+      </c>
+      <c r="Q301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>36</v>
       </c>
@@ -14690,8 +16502,14 @@
       <c r="O302">
         <v>1.0556993100000001</v>
       </c>
-    </row>
-    <row r="303" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P302">
+        <v>2.488372</v>
+      </c>
+      <c r="Q302">
+        <v>-0.20256270284613301</v>
+      </c>
+    </row>
+    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>36</v>
       </c>
@@ -14737,8 +16555,14 @@
       <c r="O303">
         <v>1.68020462</v>
       </c>
-    </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P303">
+        <v>1.7906979999999999</v>
+      </c>
+      <c r="Q303">
+        <v>-1.3699835771117901</v>
+      </c>
+    </row>
+    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>36</v>
       </c>
@@ -14784,8 +16608,14 @@
       <c r="O304">
         <v>0.40920358000000001</v>
       </c>
-    </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P304">
+        <v>2.127907</v>
+      </c>
+      <c r="Q304">
+        <v>0.303001243450439</v>
+      </c>
+    </row>
+    <row r="305" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>36</v>
       </c>
@@ -14831,8 +16661,14 @@
       <c r="O305">
         <v>0.54692258999999999</v>
       </c>
-    </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P305">
+        <v>2.104651</v>
+      </c>
+      <c r="Q305">
+        <v>-1.0211700322950199</v>
+      </c>
+    </row>
+    <row r="306" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>36</v>
       </c>
@@ -14877,6 +16713,12 @@
       </c>
       <c r="O306">
         <v>0.92729461000000002</v>
+      </c>
+      <c r="P306">
+        <v>2.7906979999999999</v>
+      </c>
+      <c r="Q306">
+        <v>5.6897249993155602E-3</v>
       </c>
     </row>
   </sheetData>

--- a/df.xlsx
+++ b/df.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stoces\Documents\Cesky_Hradek\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EC957D-9FBA-4DA3-A119-E4CFEFE56B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2739A767-7EE0-40EF-BD8A-CCE0207FDA3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
